--- a/banking_forms/013_home_loan_application--banking_forms.xlsx
+++ b/banking_forms/013_home_loan_application--banking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>credit_score</t>
+          <t>credit_score_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Credit Score</t>
+          <t>Credit Score 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>property_type</t>
+          <t>property_type_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Property Type</t>
+          <t>Property Type 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>loan_amount</t>
+          <t>loan_amount_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Loan Amount</t>
+          <t>Loan Amount 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>employment_length</t>
+          <t>employment_length_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Employment Length</t>
+          <t>Employment Length 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>interest_rate</t>
+          <t>interest_rate_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Interest Rate</t>
+          <t>Interest Rate 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>property_value</t>
+          <t>property_value_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Property Value</t>
+          <t>Property Value 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>loan_term</t>
+          <t>loan_term_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Loan Term</t>
+          <t>Loan Term 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'employed',_'label':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'employed', 'label': 'Employed'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'unemployed',_'label':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'unemployed', 'label': 'Unemployed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'salaried',_'label':_'salaried'}</t>
+          <t>salaried</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'salaried', 'label': 'Salaried'}</t>
+          <t>Salaried</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'self_employed',_'label':_'self-employed'}</t>
+          <t>self-employed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'self_employed', 'label': 'Self-Employed'}</t>
+          <t>Self-Employed</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'single_family',_'label':_'single_family'}</t>
+          <t>single_family</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'single_family', 'label': 'Single Family'}</t>
+          <t>Single Family</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'multi_family',_'label':_'multi-family'}</t>
+          <t>multi-family</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'multi_family', 'label': 'Multi-Family'}</t>
+          <t>Multi-Family</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'condo',_'label':_'condo'}</t>
+          <t>condo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'condo', 'label': 'Condo'}</t>
+          <t>Condo</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_12,_'label':_12}</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 12, 'label': 12}</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_24,_'label':_24}</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 24, 'label': 24}</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_36,_'label':_36}</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 36, 'label': 36}</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_48,_'label':_48}</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 48, 'label': 48}</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pending',_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'pending', 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'approved',_'label':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'approved', 'label': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'denied',_'label':_'denied'}</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'denied', 'label': 'Denied'}</t>
+          <t>Denied</t>
         </is>
       </c>
     </row>
@@ -1369,131 +1369,131 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'paid_off',_'label':_'paid_off'}</t>
+          <t>paid_off</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'paid_off', 'label': 'Paid Off'}</t>
+          <t>Paid Off</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>property_type_choices</t>
+          <t>property_type_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'single_family',_'label':_'single_family'}</t>
+          <t>single_family</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'single_family', 'label': 'Single Family'}</t>
+          <t>Single Family</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>property_type_choices</t>
+          <t>property_type_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'multi_family',_'label':_'multi-family'}</t>
+          <t>multi-family</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'multi_family', 'label': 'Multi-Family'}</t>
+          <t>Multi-Family</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>property_type_choices</t>
+          <t>property_type_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'condo',_'label':_'condo'}</t>
+          <t>condo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'condo', 'label': 'Condo'}</t>
+          <t>Condo</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>loan_term_choices</t>
+          <t>loan_term_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_12,_'label':_12}</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 12, 'label': 12}</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>loan_term_choices</t>
+          <t>loan_term_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_24,_'label':_24}</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 24, 'label': 24}</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>loan_term_choices</t>
+          <t>loan_term_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_36,_'label':_36}</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 36, 'label': 36}</t>
+          <t>36</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>loan_term_choices</t>
+          <t>loan_term_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_48,_'label':_48}</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 48, 'label': 48}</t>
+          <t>48</t>
         </is>
       </c>
     </row>
